--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG - Relatório de Recusas  14.07.2025 a 20.07.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG - Relatório de Recusas  14.07.2025 a 20.07.2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0600435B-0FBC-4BCB-88E6-47C45D7E8D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31BF07D3-070B-4087-A793-D74CB668AC4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="35">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,76 +54,85 @@
     <t>Relatório de Recusas  14.07.2025 a 20.07.2025</t>
   </si>
   <si>
-    <t>v</t>
-  </si>
-  <si>
-    <t>133366990</t>
+    <t>133316645</t>
   </si>
   <si>
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório Recusas Santander- 17.07.2025</t>
-  </si>
-  <si>
-    <t>133343731</t>
-  </si>
-  <si>
-    <t>133424619</t>
-  </si>
-  <si>
-    <t>133425743</t>
-  </si>
-  <si>
-    <t>133345038</t>
-  </si>
-  <si>
-    <t>133450029</t>
-  </si>
-  <si>
-    <t>133436196</t>
-  </si>
-  <si>
-    <t>133457404</t>
-  </si>
-  <si>
-    <t>133467509</t>
-  </si>
-  <si>
-    <t>133274775</t>
-  </si>
-  <si>
-    <t>133475431</t>
-  </si>
-  <si>
-    <t>133374552</t>
-  </si>
-  <si>
-    <t>133283832</t>
-  </si>
-  <si>
-    <t>133271654</t>
-  </si>
-  <si>
-    <t>133338929</t>
-  </si>
-  <si>
-    <t>133338951</t>
-  </si>
-  <si>
-    <t>133351843</t>
-  </si>
-  <si>
-    <t>133349867</t>
-  </si>
-  <si>
-    <t>133350572</t>
-  </si>
-  <si>
-    <t>133351673</t>
-  </si>
-  <si>
-    <t>133352035</t>
+    <t>Relatório Recusas Santander- 18 e 19.07.2025</t>
+  </si>
+  <si>
+    <t>133398321</t>
+  </si>
+  <si>
+    <t>133388251</t>
+  </si>
+  <si>
+    <t>133396557</t>
+  </si>
+  <si>
+    <t>133453084</t>
+  </si>
+  <si>
+    <t>133375356</t>
+  </si>
+  <si>
+    <t>133482585</t>
+  </si>
+  <si>
+    <t>133389633</t>
+  </si>
+  <si>
+    <t>133302725</t>
+  </si>
+  <si>
+    <t>133361215</t>
+  </si>
+  <si>
+    <t>133363825</t>
+  </si>
+  <si>
+    <t>133365693</t>
+  </si>
+  <si>
+    <t>133366936</t>
+  </si>
+  <si>
+    <t>133369748</t>
+  </si>
+  <si>
+    <t>133373236</t>
+  </si>
+  <si>
+    <t>133373368</t>
+  </si>
+  <si>
+    <t>133321398</t>
+  </si>
+  <si>
+    <t>133332609</t>
+  </si>
+  <si>
+    <t>133322043</t>
+  </si>
+  <si>
+    <t>133284117</t>
+  </si>
+  <si>
+    <t>133323954</t>
+  </si>
+  <si>
+    <t>133324576</t>
+  </si>
+  <si>
+    <t>133323145</t>
+  </si>
+  <si>
+    <t>133317324</t>
+  </si>
+  <si>
+    <t>133321828</t>
   </si>
 </sst>
 </file>
@@ -530,7 +539,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F1048576"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -562,13 +571,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>7</v>
@@ -580,13 +589,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>7</v>
@@ -598,13 +607,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>7</v>
@@ -616,13 +625,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>7</v>
@@ -634,13 +643,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>7</v>
@@ -652,13 +661,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>7</v>
@@ -670,13 +679,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>7</v>
@@ -688,15 +697,15 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -706,15 +715,15 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>7</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -724,13 +733,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>7</v>
@@ -742,13 +751,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>7</v>
@@ -760,13 +769,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>7</v>
@@ -778,13 +787,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>7</v>
@@ -796,13 +805,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>7</v>
@@ -814,15 +823,15 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E16" s="2" t="s">
@@ -832,15 +841,15 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>7</v>
       </c>
       <c r="E17" s="2" t="s">
@@ -850,13 +859,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>7</v>
@@ -867,13 +876,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>7</v>
@@ -884,13 +893,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>7</v>
@@ -901,13 +910,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>7</v>
@@ -918,28 +927,97 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D23" s="6"/>
-    </row>
-    <row r="1048576" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D1048576" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="B23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D27" s="6"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D28" s="6"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D29" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
